--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -428,7 +428,7 @@
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -537,11 +537,6 @@
           <t>KROGER</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
-        </is>
-      </c>
       <c r="D2" t="n">
         <v>64380020101</v>
       </c>
@@ -556,18 +551,6 @@
       </c>
       <c r="H2" t="n">
         <v>363</v>
-      </c>
-      <c r="J2" t="n">
-        <v>504</v>
-      </c>
-      <c r="K2" t="n">
-        <v>360</v>
-      </c>
-      <c r="L2" t="n">
-        <v>288</v>
-      </c>
-      <c r="M2" t="n">
-        <v>384</v>
       </c>
     </row>
     <row r="3">
@@ -581,9 +564,6 @@
           <t>KROGER</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v/>
-      </c>
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
@@ -598,18 +578,6 @@
       </c>
       <c r="H3" t="n">
         <v>122</v>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -693,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -705,10 +673,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -752,7 +720,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales Summary'!$A$1:$P$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Audit'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exceptions'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exceptions'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -537,6 +537,11 @@
           <t>KROGER</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>64380020101KROGER</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>64380020101</v>
       </c>
@@ -551,6 +556,18 @@
       </c>
       <c r="H2" t="n">
         <v>363</v>
+      </c>
+      <c r="J2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K2" t="n">
+        <v>72</v>
+      </c>
+      <c r="L2" t="n">
+        <v>696</v>
+      </c>
+      <c r="M2" t="n">
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -564,6 +581,11 @@
           <t>KROGER</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>64380018701KROGER</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
@@ -578,6 +600,18 @@
       </c>
       <c r="H3" t="n">
         <v>122</v>
+      </c>
+      <c r="J3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>240</v>
+      </c>
+      <c r="M3" t="n">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +695,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -673,10 +707,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -694,10 +728,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -713,18 +747,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MISSING_HISTORICAL_SALES</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:B1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -569,6 +569,11 @@
       <c r="M2" t="n">
         <v>296</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Econdisc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +617,11 @@
       </c>
       <c r="M3" t="n">
         <v>128</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Econdisc</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -9,12 +9,14 @@
   <sheets>
     <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Audit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Exceptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SC_Comments_Exceptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales Summary'!$A$1:$P$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Audit'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exceptions'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SC_Comments_Exceptions'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Exceptions'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,6 +740,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Normalized NDC</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>64380018701</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>64380018701</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KROGER</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NDC not present in the Critical Inventory (CIP) source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>64380020101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>64380020101</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KROGER</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NDC not present in the Critical Inventory (CIP) source</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -548,7 +548,7 @@
         <v>64380020101</v>
       </c>
       <c r="E2" t="n">
-        <v>21888</v>
+        <v>21624</v>
       </c>
       <c r="F2" t="n">
         <v>168</v>

--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -548,7 +548,7 @@
         <v>64380020101</v>
       </c>
       <c r="E2" t="n">
-        <v>21624</v>
+        <v>20976</v>
       </c>
       <c r="F2" t="n">
         <v>168</v>
@@ -597,7 +597,7 @@
         <v>64380018701</v>
       </c>
       <c r="E3" t="n">
-        <v/>
+        <v>-24</v>
       </c>
       <c r="F3" t="n">
         <v>96</v>

--- a/OrderbookAutomation/output/Sales_Summary.xlsx
+++ b/OrderbookAutomation/output/Sales_Summary.xlsx
@@ -37,12 +37,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -596,8 +603,8 @@
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
-      <c r="E3" t="n">
-        <v>-24</v>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>96</v>
